--- a/artfynd/A 44065-2022 artfynd.xlsx
+++ b/artfynd/A 44065-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44065-2022 artfynd.xlsx
+++ b/artfynd/A 44065-2022 artfynd.xlsx
@@ -9939,10 +9939,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121087308</v>
+        <v>121086346</v>
       </c>
       <c r="B84" t="n">
-        <v>90683</v>
+        <v>55950</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9955,37 +9955,41 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1108</v>
+        <v>206004</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>541971</v>
+        <v>541868</v>
       </c>
       <c r="R84" t="n">
-        <v>7208368</v>
+        <v>7208253</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10014,7 +10018,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10024,7 +10028,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10039,22 +10043,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121086346</v>
+        <v>121087308</v>
       </c>
       <c r="B85" t="n">
-        <v>55950</v>
+        <v>90683</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10067,41 +10071,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>206004</v>
+        <v>1108</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541868</v>
+        <v>541971</v>
       </c>
       <c r="R85" t="n">
-        <v>7208253</v>
+        <v>7208368</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10155,12 +10155,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 44065-2022 artfynd.xlsx
+++ b/artfynd/A 44065-2022 artfynd.xlsx
@@ -9374,10 +9374,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121087301</v>
+        <v>121087292</v>
       </c>
       <c r="B79" t="n">
-        <v>57348</v>
+        <v>90711</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9390,39 +9390,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541941</v>
+        <v>541850</v>
       </c>
       <c r="R79" t="n">
-        <v>7208347</v>
+        <v>7208245</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9454,7 +9449,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9464,7 +9459,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9491,10 +9486,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121087298</v>
+        <v>121087303</v>
       </c>
       <c r="B80" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9507,34 +9502,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541890</v>
+        <v>541947</v>
       </c>
       <c r="R80" t="n">
-        <v>7208300</v>
+        <v>7208367</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9603,10 +9603,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121087306</v>
+        <v>121087304</v>
       </c>
       <c r="B81" t="n">
-        <v>91042</v>
+        <v>57351</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9615,38 +9615,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541965</v>
+        <v>541955</v>
       </c>
       <c r="R81" t="n">
-        <v>7208367</v>
+        <v>7208354</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9678,7 +9683,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9688,7 +9693,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9715,10 +9720,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121087292</v>
+        <v>121087307</v>
       </c>
       <c r="B82" t="n">
-        <v>90701</v>
+        <v>91137</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9727,25 +9732,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9755,10 +9760,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541850</v>
+        <v>541966</v>
       </c>
       <c r="R82" t="n">
-        <v>7208245</v>
+        <v>7208365</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9790,7 +9795,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9800,7 +9805,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9827,10 +9832,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121087299</v>
+        <v>121087308</v>
       </c>
       <c r="B83" t="n">
-        <v>90705</v>
+        <v>90693</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9843,21 +9848,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9867,10 +9872,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>541906</v>
+        <v>541971</v>
       </c>
       <c r="R83" t="n">
-        <v>7208324</v>
+        <v>7208368</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9902,7 +9907,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9912,7 +9917,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9939,10 +9944,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121086346</v>
+        <v>121087294</v>
       </c>
       <c r="B84" t="n">
-        <v>55950</v>
+        <v>90711</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9955,41 +9960,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>206004</v>
+        <v>1204</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>541868</v>
+        <v>541831</v>
       </c>
       <c r="R84" t="n">
-        <v>7208253</v>
+        <v>7208244</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10043,22 +10044,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121087308</v>
+        <v>121087305</v>
       </c>
       <c r="B85" t="n">
-        <v>90683</v>
+        <v>90697</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10071,21 +10072,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10095,10 +10096,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541971</v>
+        <v>541965</v>
       </c>
       <c r="R85" t="n">
-        <v>7208368</v>
+        <v>7208372</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10130,7 +10131,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10140,7 +10141,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10167,10 +10168,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121087303</v>
+        <v>121087300</v>
       </c>
       <c r="B86" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10212,10 +10213,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541947</v>
+        <v>541932</v>
       </c>
       <c r="R86" t="n">
-        <v>7208367</v>
+        <v>7208314</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10247,7 +10248,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10257,7 +10258,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10284,10 +10285,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121087421</v>
+        <v>121087302</v>
       </c>
       <c r="B87" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10318,27 +10319,24 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541876</v>
+        <v>541945</v>
       </c>
       <c r="R87" t="n">
-        <v>7208263</v>
+        <v>7208373</v>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10367,7 +10365,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10377,7 +10375,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10392,22 +10390,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121087302</v>
+        <v>121087298</v>
       </c>
       <c r="B88" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10420,39 +10418,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541945</v>
+        <v>541890</v>
       </c>
       <c r="R88" t="n">
-        <v>7208373</v>
+        <v>7208300</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10484,7 +10477,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10494,7 +10487,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10521,10 +10514,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121087300</v>
+        <v>121087299</v>
       </c>
       <c r="B89" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10537,39 +10530,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541932</v>
+        <v>541906</v>
       </c>
       <c r="R89" t="n">
-        <v>7208314</v>
+        <v>7208324</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10601,7 +10589,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10611,7 +10599,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10638,10 +10626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121087293</v>
+        <v>121087295</v>
       </c>
       <c r="B90" t="n">
-        <v>57348</v>
+        <v>90697</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10654,29 +10642,24 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
@@ -10755,10 +10738,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121087305</v>
+        <v>121086346</v>
       </c>
       <c r="B91" t="n">
-        <v>90687</v>
+        <v>55953</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10771,37 +10754,41 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541965</v>
+        <v>541868</v>
       </c>
       <c r="R91" t="n">
-        <v>7208372</v>
+        <v>7208253</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10830,7 +10817,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10840,7 +10827,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10855,22 +10842,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121087307</v>
+        <v>121086332</v>
       </c>
       <c r="B92" t="n">
-        <v>91127</v>
+        <v>57351</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10879,41 +10866,49 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541966</v>
+        <v>541849</v>
       </c>
       <c r="R92" t="n">
-        <v>7208365</v>
+        <v>7208291</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10942,7 +10937,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10952,7 +10947,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10963,26 +10963,46 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121087295</v>
+        <v>121087421</v>
       </c>
       <c r="B93" t="n">
-        <v>90687</v>
+        <v>57351</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10995,37 +11015,45 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541831</v>
+        <v>541876</v>
       </c>
       <c r="R93" t="n">
-        <v>7208244</v>
+        <v>7208263</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11054,7 +11082,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11064,7 +11092,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11079,22 +11107,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121086332</v>
+        <v>121087301</v>
       </c>
       <c r="B94" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11125,27 +11153,24 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541849</v>
+        <v>541941</v>
       </c>
       <c r="R94" t="n">
-        <v>7208291</v>
+        <v>7208347</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11174,7 +11199,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11184,12 +11209,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11200,46 +11220,26 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121087304</v>
+        <v>121086333</v>
       </c>
       <c r="B95" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11270,24 +11270,27 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541955</v>
+        <v>541904</v>
       </c>
       <c r="R95" t="n">
-        <v>7208354</v>
+        <v>7208324</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11316,7 +11319,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11326,7 +11329,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11337,26 +11345,46 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121087297</v>
+        <v>121087306</v>
       </c>
       <c r="B96" t="n">
-        <v>90705</v>
+        <v>91052</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11365,25 +11393,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11393,10 +11421,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541887</v>
+        <v>541965</v>
       </c>
       <c r="R96" t="n">
-        <v>7208302</v>
+        <v>7208367</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11428,7 +11456,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11438,7 +11466,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11465,10 +11493,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121087294</v>
+        <v>121087297</v>
       </c>
       <c r="B97" t="n">
-        <v>90701</v>
+        <v>90715</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11481,21 +11509,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11505,10 +11533,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541831</v>
+        <v>541887</v>
       </c>
       <c r="R97" t="n">
-        <v>7208244</v>
+        <v>7208302</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11540,7 +11568,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11550,7 +11578,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11577,10 +11605,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121086333</v>
+        <v>121087293</v>
       </c>
       <c r="B98" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11611,27 +11639,24 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541904</v>
+        <v>541831</v>
       </c>
       <c r="R98" t="n">
-        <v>7208324</v>
+        <v>7208244</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11660,7 +11685,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11670,12 +11695,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11686,36 +11706,16 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>

--- a/artfynd/A 44065-2022 artfynd.xlsx
+++ b/artfynd/A 44065-2022 artfynd.xlsx
@@ -9374,10 +9374,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121087292</v>
+        <v>121087301</v>
       </c>
       <c r="B79" t="n">
-        <v>90711</v>
+        <v>57351</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9390,34 +9390,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541850</v>
+        <v>541941</v>
       </c>
       <c r="R79" t="n">
-        <v>7208245</v>
+        <v>7208347</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9449,7 +9454,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9459,7 +9464,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9486,7 +9491,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121087303</v>
+        <v>121086333</v>
       </c>
       <c r="B80" t="n">
         <v>57351</v>
@@ -9520,24 +9525,27 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541947</v>
+        <v>541904</v>
       </c>
       <c r="R80" t="n">
-        <v>7208367</v>
+        <v>7208324</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9566,7 +9574,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9576,7 +9584,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9587,26 +9600,46 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121087304</v>
+        <v>121087307</v>
       </c>
       <c r="B81" t="n">
-        <v>57351</v>
+        <v>91137</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9615,43 +9648,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541955</v>
+        <v>541966</v>
       </c>
       <c r="R81" t="n">
-        <v>7208354</v>
+        <v>7208365</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9683,7 +9711,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9693,7 +9721,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9720,10 +9748,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121087307</v>
+        <v>121087298</v>
       </c>
       <c r="B82" t="n">
-        <v>91137</v>
+        <v>78601</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9732,25 +9760,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9760,10 +9788,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541966</v>
+        <v>541890</v>
       </c>
       <c r="R82" t="n">
-        <v>7208365</v>
+        <v>7208300</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9795,7 +9823,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9805,7 +9833,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9832,10 +9860,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121087308</v>
+        <v>121087293</v>
       </c>
       <c r="B83" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9848,34 +9876,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>541971</v>
+        <v>541831</v>
       </c>
       <c r="R83" t="n">
-        <v>7208368</v>
+        <v>7208244</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9907,7 +9940,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9917,7 +9950,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9944,10 +9977,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121087294</v>
+        <v>121087421</v>
       </c>
       <c r="B84" t="n">
-        <v>90711</v>
+        <v>57351</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9960,37 +9993,45 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>541831</v>
+        <v>541876</v>
       </c>
       <c r="R84" t="n">
-        <v>7208244</v>
+        <v>7208263</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10019,7 +10060,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10029,7 +10070,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10044,22 +10085,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121087305</v>
+        <v>121087308</v>
       </c>
       <c r="B85" t="n">
-        <v>90697</v>
+        <v>90693</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10072,21 +10113,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10096,10 +10137,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541965</v>
+        <v>541971</v>
       </c>
       <c r="R85" t="n">
-        <v>7208372</v>
+        <v>7208368</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10131,7 +10172,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10141,7 +10182,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10168,10 +10209,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121087300</v>
+        <v>121087297</v>
       </c>
       <c r="B86" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10184,39 +10225,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541932</v>
+        <v>541887</v>
       </c>
       <c r="R86" t="n">
-        <v>7208314</v>
+        <v>7208302</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10248,7 +10284,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10258,7 +10294,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10285,10 +10321,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121087302</v>
+        <v>121087306</v>
       </c>
       <c r="B87" t="n">
-        <v>57351</v>
+        <v>91052</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10297,43 +10333,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541945</v>
+        <v>541965</v>
       </c>
       <c r="R87" t="n">
-        <v>7208373</v>
+        <v>7208367</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10365,7 +10396,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10375,7 +10406,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10402,10 +10433,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121087298</v>
+        <v>121087304</v>
       </c>
       <c r="B88" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10418,34 +10449,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541890</v>
+        <v>541955</v>
       </c>
       <c r="R88" t="n">
-        <v>7208300</v>
+        <v>7208354</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10477,7 +10513,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10487,7 +10523,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10514,10 +10550,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121087299</v>
+        <v>121086346</v>
       </c>
       <c r="B89" t="n">
-        <v>90715</v>
+        <v>55953</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10530,37 +10566,41 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>206004</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541906</v>
+        <v>541868</v>
       </c>
       <c r="R89" t="n">
-        <v>7208324</v>
+        <v>7208253</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10589,7 +10629,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10599,7 +10639,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10614,22 +10654,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121087295</v>
+        <v>121087294</v>
       </c>
       <c r="B90" t="n">
-        <v>90697</v>
+        <v>90711</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10642,21 +10682,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10738,10 +10778,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121086346</v>
+        <v>121087305</v>
       </c>
       <c r="B91" t="n">
-        <v>55953</v>
+        <v>90697</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10754,41 +10794,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541868</v>
+        <v>541965</v>
       </c>
       <c r="R91" t="n">
-        <v>7208253</v>
+        <v>7208372</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10817,7 +10853,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10827,7 +10863,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10842,22 +10878,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121086332</v>
+        <v>121087292</v>
       </c>
       <c r="B92" t="n">
-        <v>57351</v>
+        <v>90711</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10870,45 +10906,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541849</v>
+        <v>541850</v>
       </c>
       <c r="R92" t="n">
-        <v>7208291</v>
+        <v>7208245</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10937,7 +10965,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10947,12 +10975,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10963,43 +10986,23 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121087421</v>
+        <v>121086332</v>
       </c>
       <c r="B93" t="n">
         <v>57351</v>
@@ -11037,23 +11040,23 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541876</v>
+        <v>541849</v>
       </c>
       <c r="R93" t="n">
-        <v>7208263</v>
+        <v>7208291</v>
       </c>
       <c r="S93" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11082,7 +11085,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11092,7 +11095,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11103,23 +11111,43 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121087301</v>
+        <v>121087300</v>
       </c>
       <c r="B94" t="n">
         <v>57351</v>
@@ -11155,7 +11183,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11164,10 +11192,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541941</v>
+        <v>541932</v>
       </c>
       <c r="R94" t="n">
-        <v>7208347</v>
+        <v>7208314</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11199,7 +11227,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11209,7 +11237,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11236,7 +11264,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121086333</v>
+        <v>121087303</v>
       </c>
       <c r="B95" t="n">
         <v>57351</v>
@@ -11270,27 +11298,24 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541904</v>
+        <v>541947</v>
       </c>
       <c r="R95" t="n">
-        <v>7208324</v>
+        <v>7208367</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11319,7 +11344,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11329,12 +11354,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11345,46 +11365,26 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121087306</v>
+        <v>121087299</v>
       </c>
       <c r="B96" t="n">
-        <v>91052</v>
+        <v>90715</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11393,25 +11393,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11421,10 +11421,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541965</v>
+        <v>541906</v>
       </c>
       <c r="R96" t="n">
-        <v>7208367</v>
+        <v>7208324</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11493,10 +11493,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121087297</v>
+        <v>121087295</v>
       </c>
       <c r="B97" t="n">
-        <v>90715</v>
+        <v>90697</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11509,21 +11509,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11533,10 +11533,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541887</v>
+        <v>541831</v>
       </c>
       <c r="R97" t="n">
-        <v>7208302</v>
+        <v>7208244</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11578,7 +11578,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11605,7 +11605,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121087293</v>
+        <v>121087302</v>
       </c>
       <c r="B98" t="n">
         <v>57351</v>
@@ -11641,7 +11641,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541831</v>
+        <v>541945</v>
       </c>
       <c r="R98" t="n">
-        <v>7208244</v>
+        <v>7208373</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 44065-2022 artfynd.xlsx
+++ b/artfynd/A 44065-2022 artfynd.xlsx
@@ -10321,10 +10321,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121087306</v>
+        <v>121086346</v>
       </c>
       <c r="B87" t="n">
-        <v>91052</v>
+        <v>55953</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10333,41 +10333,45 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1506</v>
+        <v>206004</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541965</v>
+        <v>541868</v>
       </c>
       <c r="R87" t="n">
-        <v>7208367</v>
+        <v>7208253</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10396,7 +10400,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10406,7 +10410,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10421,22 +10425,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121087304</v>
+        <v>121087306</v>
       </c>
       <c r="B88" t="n">
-        <v>57351</v>
+        <v>91052</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10445,43 +10449,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541955</v>
+        <v>541965</v>
       </c>
       <c r="R88" t="n">
-        <v>7208354</v>
+        <v>7208367</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10513,7 +10512,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10523,7 +10522,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10550,10 +10549,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121086346</v>
+        <v>121087304</v>
       </c>
       <c r="B89" t="n">
-        <v>55953</v>
+        <v>57351</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10566,41 +10565,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541868</v>
+        <v>541955</v>
       </c>
       <c r="R89" t="n">
-        <v>7208253</v>
+        <v>7208354</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10654,22 +10654,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121087294</v>
+        <v>121087305</v>
       </c>
       <c r="B90" t="n">
-        <v>90711</v>
+        <v>90697</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10682,21 +10682,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10706,10 +10706,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541831</v>
+        <v>541965</v>
       </c>
       <c r="R90" t="n">
-        <v>7208244</v>
+        <v>7208372</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10741,7 +10741,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10778,10 +10778,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121087305</v>
+        <v>121087294</v>
       </c>
       <c r="B91" t="n">
-        <v>90697</v>
+        <v>90711</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10794,21 +10794,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541965</v>
+        <v>541831</v>
       </c>
       <c r="R91" t="n">
-        <v>7208372</v>
+        <v>7208244</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10853,7 +10853,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 44065-2022 artfynd.xlsx
+++ b/artfynd/A 44065-2022 artfynd.xlsx
@@ -9374,7 +9374,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121087301</v>
+        <v>121087304</v>
       </c>
       <c r="B79" t="n">
         <v>57351</v>
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541941</v>
+        <v>541955</v>
       </c>
       <c r="R79" t="n">
-        <v>7208347</v>
+        <v>7208354</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9491,10 +9491,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121086333</v>
+        <v>121087307</v>
       </c>
       <c r="B80" t="n">
-        <v>57351</v>
+        <v>91149</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9503,49 +9503,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541904</v>
+        <v>541966</v>
       </c>
       <c r="R80" t="n">
-        <v>7208324</v>
+        <v>7208365</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9574,7 +9566,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9584,12 +9576,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9600,46 +9587,26 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121087307</v>
+        <v>121087292</v>
       </c>
       <c r="B81" t="n">
-        <v>91137</v>
+        <v>90723</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9648,25 +9615,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9676,10 +9643,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541966</v>
+        <v>541850</v>
       </c>
       <c r="R81" t="n">
-        <v>7208365</v>
+        <v>7208245</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9711,7 +9678,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9721,7 +9688,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9748,10 +9715,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121087298</v>
+        <v>121087293</v>
       </c>
       <c r="B82" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9764,34 +9731,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541890</v>
+        <v>541831</v>
       </c>
       <c r="R82" t="n">
-        <v>7208300</v>
+        <v>7208244</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9823,7 +9795,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9833,7 +9805,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9860,7 +9832,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121087293</v>
+        <v>121087302</v>
       </c>
       <c r="B83" t="n">
         <v>57351</v>
@@ -9896,7 +9868,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9905,10 +9877,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>541831</v>
+        <v>541945</v>
       </c>
       <c r="R83" t="n">
-        <v>7208244</v>
+        <v>7208373</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9940,7 +9912,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9950,7 +9922,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9977,10 +9949,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121087421</v>
+        <v>121087294</v>
       </c>
       <c r="B84" t="n">
-        <v>57351</v>
+        <v>90723</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9993,45 +9965,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>541876</v>
+        <v>541831</v>
       </c>
       <c r="R84" t="n">
-        <v>7208263</v>
+        <v>7208244</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10060,7 +10024,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10070,7 +10034,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10085,22 +10049,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121087308</v>
+        <v>121087305</v>
       </c>
       <c r="B85" t="n">
-        <v>90693</v>
+        <v>90709</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10113,21 +10077,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10137,10 +10101,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541971</v>
+        <v>541965</v>
       </c>
       <c r="R85" t="n">
-        <v>7208368</v>
+        <v>7208372</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10172,7 +10136,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10182,7 +10146,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10209,10 +10173,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121087297</v>
+        <v>121087306</v>
       </c>
       <c r="B86" t="n">
-        <v>90715</v>
+        <v>91064</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10221,25 +10185,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10249,10 +10213,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541887</v>
+        <v>541965</v>
       </c>
       <c r="R86" t="n">
-        <v>7208302</v>
+        <v>7208367</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10284,7 +10248,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10294,7 +10258,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10321,10 +10285,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121086346</v>
+        <v>121087303</v>
       </c>
       <c r="B87" t="n">
-        <v>55953</v>
+        <v>57351</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10337,41 +10301,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541868</v>
+        <v>541947</v>
       </c>
       <c r="R87" t="n">
-        <v>7208253</v>
+        <v>7208367</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10400,7 +10365,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10410,7 +10375,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10425,22 +10390,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121087306</v>
+        <v>121086332</v>
       </c>
       <c r="B88" t="n">
-        <v>91052</v>
+        <v>57351</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10449,41 +10414,49 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541965</v>
+        <v>541849</v>
       </c>
       <c r="R88" t="n">
-        <v>7208367</v>
+        <v>7208291</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10512,7 +10485,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10522,7 +10495,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10533,23 +10511,43 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121087304</v>
+        <v>121086333</v>
       </c>
       <c r="B89" t="n">
         <v>57351</v>
@@ -10583,24 +10581,27 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541955</v>
+        <v>541904</v>
       </c>
       <c r="R89" t="n">
-        <v>7208354</v>
+        <v>7208324</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10629,7 +10630,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10639,7 +10640,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10650,26 +10656,46 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121087305</v>
+        <v>121087297</v>
       </c>
       <c r="B90" t="n">
-        <v>90697</v>
+        <v>90727</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10682,21 +10708,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10706,10 +10732,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541965</v>
+        <v>541887</v>
       </c>
       <c r="R90" t="n">
-        <v>7208372</v>
+        <v>7208302</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10741,7 +10767,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10751,7 +10777,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10778,10 +10804,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121087294</v>
+        <v>121087299</v>
       </c>
       <c r="B91" t="n">
-        <v>90711</v>
+        <v>90727</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10794,21 +10820,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10818,10 +10844,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541831</v>
+        <v>541906</v>
       </c>
       <c r="R91" t="n">
-        <v>7208244</v>
+        <v>7208324</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10853,7 +10879,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10863,7 +10889,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10890,10 +10916,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121087292</v>
+        <v>121087308</v>
       </c>
       <c r="B92" t="n">
-        <v>90711</v>
+        <v>90705</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10906,21 +10932,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10930,10 +10956,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541850</v>
+        <v>541971</v>
       </c>
       <c r="R92" t="n">
-        <v>7208245</v>
+        <v>7208368</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10965,7 +10991,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10975,7 +11001,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11002,10 +11028,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121086332</v>
+        <v>121086346</v>
       </c>
       <c r="B93" t="n">
-        <v>57351</v>
+        <v>55953</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11018,42 +11044,38 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541849</v>
+        <v>541868</v>
       </c>
       <c r="R93" t="n">
-        <v>7208291</v>
+        <v>7208253</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11085,7 +11107,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11095,12 +11117,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11111,26 +11128,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11140,17 +11137,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121087300</v>
+        <v>121087295</v>
       </c>
       <c r="B94" t="n">
-        <v>57351</v>
+        <v>90709</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11163,39 +11160,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541932</v>
+        <v>541831</v>
       </c>
       <c r="R94" t="n">
-        <v>7208314</v>
+        <v>7208244</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11227,7 +11219,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11237,7 +11229,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11264,7 +11256,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121087303</v>
+        <v>121087301</v>
       </c>
       <c r="B95" t="n">
         <v>57351</v>
@@ -11300,7 +11292,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11309,10 +11301,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541947</v>
+        <v>541941</v>
       </c>
       <c r="R95" t="n">
-        <v>7208367</v>
+        <v>7208347</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11344,7 +11336,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11354,7 +11346,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11381,10 +11373,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121087299</v>
+        <v>121087300</v>
       </c>
       <c r="B96" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11397,34 +11389,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541906</v>
+        <v>541932</v>
       </c>
       <c r="R96" t="n">
-        <v>7208324</v>
+        <v>7208314</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11456,7 +11453,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11466,7 +11463,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11493,10 +11490,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121087295</v>
+        <v>121087421</v>
       </c>
       <c r="B97" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11509,37 +11506,45 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541831</v>
+        <v>541876</v>
       </c>
       <c r="R97" t="n">
-        <v>7208244</v>
+        <v>7208263</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11568,7 +11573,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11578,7 +11583,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11593,22 +11598,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121087302</v>
+        <v>121087298</v>
       </c>
       <c r="B98" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11621,39 +11626,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541945</v>
+        <v>541890</v>
       </c>
       <c r="R98" t="n">
-        <v>7208373</v>
+        <v>7208300</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 44065-2022 artfynd.xlsx
+++ b/artfynd/A 44065-2022 artfynd.xlsx
@@ -9374,10 +9374,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121087304</v>
+        <v>121087295</v>
       </c>
       <c r="B79" t="n">
-        <v>57351</v>
+        <v>90710</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9390,39 +9390,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541955</v>
+        <v>541831</v>
       </c>
       <c r="R79" t="n">
-        <v>7208354</v>
+        <v>7208244</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9454,7 +9449,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9464,7 +9459,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9491,10 +9486,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121087307</v>
+        <v>121086346</v>
       </c>
       <c r="B80" t="n">
-        <v>91149</v>
+        <v>55953</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9503,41 +9498,45 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>206004</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541966</v>
+        <v>541868</v>
       </c>
       <c r="R80" t="n">
-        <v>7208365</v>
+        <v>7208253</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9566,7 +9565,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9576,7 +9575,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9591,22 +9590,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121087292</v>
+        <v>121087306</v>
       </c>
       <c r="B81" t="n">
-        <v>90723</v>
+        <v>91065</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9615,25 +9614,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1204</v>
+        <v>1506</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9643,10 +9642,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541850</v>
+        <v>541965</v>
       </c>
       <c r="R81" t="n">
-        <v>7208245</v>
+        <v>7208367</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9678,7 +9677,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9688,7 +9687,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9715,10 +9714,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121087293</v>
+        <v>121087308</v>
       </c>
       <c r="B82" t="n">
-        <v>57351</v>
+        <v>90706</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9731,39 +9730,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541831</v>
+        <v>541971</v>
       </c>
       <c r="R82" t="n">
-        <v>7208244</v>
+        <v>7208368</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9795,7 +9789,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9805,7 +9799,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9832,7 +9826,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121087302</v>
+        <v>121087421</v>
       </c>
       <c r="B83" t="n">
         <v>57351</v>
@@ -9866,24 +9860,27 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>541945</v>
+        <v>541876</v>
       </c>
       <c r="R83" t="n">
-        <v>7208373</v>
+        <v>7208263</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9912,7 +9909,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9922,7 +9919,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9937,22 +9934,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121087294</v>
+        <v>121087292</v>
       </c>
       <c r="B84" t="n">
-        <v>90723</v>
+        <v>90724</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9989,10 +9986,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>541831</v>
+        <v>541850</v>
       </c>
       <c r="R84" t="n">
-        <v>7208244</v>
+        <v>7208245</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10024,7 +10021,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10034,7 +10031,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10061,10 +10058,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121087305</v>
+        <v>121087298</v>
       </c>
       <c r="B85" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10077,21 +10074,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10101,10 +10098,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541965</v>
+        <v>541890</v>
       </c>
       <c r="R85" t="n">
-        <v>7208372</v>
+        <v>7208300</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10136,7 +10133,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10146,7 +10143,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10173,10 +10170,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121087306</v>
+        <v>121087304</v>
       </c>
       <c r="B86" t="n">
-        <v>91064</v>
+        <v>57351</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10185,38 +10182,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541965</v>
+        <v>541955</v>
       </c>
       <c r="R86" t="n">
-        <v>7208367</v>
+        <v>7208354</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10248,7 +10250,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10258,7 +10260,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10285,7 +10287,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121087303</v>
+        <v>121087300</v>
       </c>
       <c r="B87" t="n">
         <v>57351</v>
@@ -10330,10 +10332,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541947</v>
+        <v>541932</v>
       </c>
       <c r="R87" t="n">
-        <v>7208367</v>
+        <v>7208314</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10365,7 +10367,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10375,7 +10377,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10402,7 +10404,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121086332</v>
+        <v>121087303</v>
       </c>
       <c r="B88" t="n">
         <v>57351</v>
@@ -10436,27 +10438,24 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541849</v>
+        <v>541947</v>
       </c>
       <c r="R88" t="n">
-        <v>7208291</v>
+        <v>7208367</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10485,7 +10484,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10495,12 +10494,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10511,43 +10505,23 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121086333</v>
+        <v>121087302</v>
       </c>
       <c r="B89" t="n">
         <v>57351</v>
@@ -10581,27 +10555,24 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541904</v>
+        <v>541945</v>
       </c>
       <c r="R89" t="n">
-        <v>7208324</v>
+        <v>7208373</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10630,7 +10601,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10640,12 +10611,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10656,46 +10622,26 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121087297</v>
+        <v>121087307</v>
       </c>
       <c r="B90" t="n">
-        <v>90727</v>
+        <v>91150</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10704,25 +10650,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10732,10 +10678,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541887</v>
+        <v>541966</v>
       </c>
       <c r="R90" t="n">
-        <v>7208302</v>
+        <v>7208365</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10767,7 +10713,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10777,7 +10723,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10807,7 +10753,7 @@
         <v>121087299</v>
       </c>
       <c r="B91" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10916,10 +10862,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121087308</v>
+        <v>121086332</v>
       </c>
       <c r="B92" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10932,37 +10878,45 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541971</v>
+        <v>541849</v>
       </c>
       <c r="R92" t="n">
-        <v>7208368</v>
+        <v>7208291</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10991,7 +10945,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11001,7 +10955,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11012,26 +10971,46 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121086346</v>
+        <v>121087294</v>
       </c>
       <c r="B93" t="n">
-        <v>55953</v>
+        <v>90724</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11044,41 +11023,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>206004</v>
+        <v>1204</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541868</v>
+        <v>541831</v>
       </c>
       <c r="R93" t="n">
-        <v>7208253</v>
+        <v>7208244</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11132,22 +11107,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121087295</v>
+        <v>121087293</v>
       </c>
       <c r="B94" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11160,24 +11135,29 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
@@ -11256,10 +11236,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121087301</v>
+        <v>121087305</v>
       </c>
       <c r="B95" t="n">
-        <v>57351</v>
+        <v>90710</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11272,39 +11252,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541941</v>
+        <v>541965</v>
       </c>
       <c r="R95" t="n">
-        <v>7208347</v>
+        <v>7208372</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11336,7 +11311,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11346,7 +11321,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11373,7 +11348,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121087300</v>
+        <v>121086333</v>
       </c>
       <c r="B96" t="n">
         <v>57351</v>
@@ -11407,24 +11382,27 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541932</v>
+        <v>541904</v>
       </c>
       <c r="R96" t="n">
-        <v>7208314</v>
+        <v>7208324</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11453,7 +11431,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11463,7 +11441,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11474,23 +11457,43 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121087421</v>
+        <v>121087301</v>
       </c>
       <c r="B97" t="n">
         <v>57351</v>
@@ -11524,27 +11527,24 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541876</v>
+        <v>541941</v>
       </c>
       <c r="R97" t="n">
-        <v>7208263</v>
+        <v>7208347</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11598,22 +11598,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121087298</v>
+        <v>121087297</v>
       </c>
       <c r="B98" t="n">
-        <v>78604</v>
+        <v>90728</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11626,21 +11626,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541890</v>
+        <v>541887</v>
       </c>
       <c r="R98" t="n">
-        <v>7208300</v>
+        <v>7208302</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 44065-2022 artfynd.xlsx
+++ b/artfynd/A 44065-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4742,10 +4742,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104580214</v>
+        <v>104580185</v>
       </c>
       <c r="B38" t="n">
-        <v>56395</v>
+        <v>89410</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4758,39 +4758,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rödingsjön NO, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542066.5764001671</v>
+        <v>541958.5585233027</v>
       </c>
       <c r="R38" t="n">
-        <v>7208522.663498325</v>
+        <v>7208671.369767522</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4822,7 +4817,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4827,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,10 +4854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104580203</v>
+        <v>104580244</v>
       </c>
       <c r="B39" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4875,39 +4870,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rödingsjön NO, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541886.4477179167</v>
+        <v>542292.5885779595</v>
       </c>
       <c r="R39" t="n">
-        <v>7208466.381632826</v>
+        <v>7208748.874324297</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4939,7 +4929,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4949,7 +4939,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4976,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>104580185</v>
+        <v>104580210</v>
       </c>
       <c r="B40" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4992,21 +4982,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5016,10 +5006,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541958.5585233027</v>
+        <v>541954.6110184087</v>
       </c>
       <c r="R40" t="n">
-        <v>7208671.369767522</v>
+        <v>7208530.395831825</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5051,7 +5041,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5061,7 +5051,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5088,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>104580244</v>
+        <v>104580221</v>
       </c>
       <c r="B41" t="n">
-        <v>77506</v>
+        <v>73698</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5104,21 +5094,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5128,10 +5118,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542292.5885779595</v>
+        <v>542100.523456649</v>
       </c>
       <c r="R41" t="n">
-        <v>7208748.874324297</v>
+        <v>7208609.049039152</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5163,7 +5153,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5173,7 +5163,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5200,7 +5190,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>104580210</v>
+        <v>104580250</v>
       </c>
       <c r="B42" t="n">
         <v>77506</v>
@@ -5240,10 +5230,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541954.6110184087</v>
+        <v>542458.4944434372</v>
       </c>
       <c r="R42" t="n">
-        <v>7208530.395831825</v>
+        <v>7208760.965456374</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5275,7 +5265,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5285,7 +5275,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5312,10 +5302,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>104580221</v>
+        <v>104580186</v>
       </c>
       <c r="B43" t="n">
-        <v>73698</v>
+        <v>89734</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5324,25 +5314,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1467</v>
+        <v>2063</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5352,10 +5342,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542100.523456649</v>
+        <v>541959.841215348</v>
       </c>
       <c r="R43" t="n">
-        <v>7208609.049039152</v>
+        <v>7208670.541485483</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5387,7 +5377,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5397,7 +5387,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5408,6 +5398,16 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>2211101311</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5424,10 +5424,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>104580250</v>
+        <v>104580240</v>
       </c>
       <c r="B44" t="n">
-        <v>77506</v>
+        <v>73693</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5440,21 +5440,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542458.4944434372</v>
+        <v>542260.1189058821</v>
       </c>
       <c r="R44" t="n">
-        <v>7208760.965456374</v>
+        <v>7208708.213468658</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5536,10 +5536,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>104580186</v>
+        <v>104580236</v>
       </c>
       <c r="B45" t="n">
-        <v>89734</v>
+        <v>89406</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5548,25 +5548,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2063</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541959.841215348</v>
+        <v>542232.0481639864</v>
       </c>
       <c r="R45" t="n">
-        <v>7208670.541485483</v>
+        <v>7208715.855759163</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5632,16 +5632,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>2211101311</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5658,10 +5648,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104580240</v>
+        <v>104580248</v>
       </c>
       <c r="B46" t="n">
-        <v>73693</v>
+        <v>77506</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5674,21 +5664,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5698,10 +5688,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542260.1189058821</v>
+        <v>542431.4996614412</v>
       </c>
       <c r="R46" t="n">
-        <v>7208708.213468658</v>
+        <v>7208752.541063905</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5733,7 +5723,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5743,7 +5733,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5770,10 +5760,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104580236</v>
+        <v>104580189</v>
       </c>
       <c r="B47" t="n">
-        <v>89406</v>
+        <v>77506</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5786,21 +5776,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5810,10 +5800,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542232.0481639864</v>
+        <v>541880.0109594867</v>
       </c>
       <c r="R47" t="n">
-        <v>7208715.855759163</v>
+        <v>7208713.428048602</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5845,7 +5835,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5855,7 +5845,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5882,10 +5872,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>104580248</v>
+        <v>104580197</v>
       </c>
       <c r="B48" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5898,21 +5888,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5922,10 +5912,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542431.4996614412</v>
+        <v>541733.6538041134</v>
       </c>
       <c r="R48" t="n">
-        <v>7208752.541063905</v>
+        <v>7208666.519942796</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5957,7 +5947,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5967,7 +5957,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5994,7 +5984,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>104580189</v>
+        <v>104580213</v>
       </c>
       <c r="B49" t="n">
         <v>77506</v>
@@ -6034,10 +6024,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541880.0109594867</v>
+        <v>542066.5764001671</v>
       </c>
       <c r="R49" t="n">
-        <v>7208713.428048602</v>
+        <v>7208522.663498325</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6069,7 +6059,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6079,7 +6069,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6106,10 +6096,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>104580197</v>
+        <v>104660087</v>
       </c>
       <c r="B50" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6122,34 +6112,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rödingsjön NO, Ås lm</t>
+          <t>Bladberget, Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541733.6538041134</v>
+        <v>542281.4243606708</v>
       </c>
       <c r="R50" t="n">
-        <v>7208666.519942796</v>
+        <v>7208699.629120762</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6181,7 +6171,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6191,7 +6181,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6206,22 +6196,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>104580213</v>
+        <v>104660069</v>
       </c>
       <c r="B51" t="n">
-        <v>77506</v>
+        <v>73698</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6234,34 +6224,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rödingsjön NO, Ås lm</t>
+          <t>Bladberget, Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542066.5764001671</v>
+        <v>541957.4411678994</v>
       </c>
       <c r="R51" t="n">
-        <v>7208522.663498325</v>
+        <v>7208389.51064281</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6293,7 +6283,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6303,7 +6293,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6318,22 +6308,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>104660087</v>
+        <v>104660081</v>
       </c>
       <c r="B52" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6346,21 +6336,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6370,10 +6360,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542281.4243606708</v>
+        <v>542027.5024151764</v>
       </c>
       <c r="R52" t="n">
-        <v>7208699.629120762</v>
+        <v>7208529.306604995</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6405,7 +6395,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6415,7 +6405,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6442,10 +6432,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>104660069</v>
+        <v>104660073</v>
       </c>
       <c r="B53" t="n">
-        <v>73698</v>
+        <v>77588</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6458,21 +6448,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6482,10 +6472,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541957.4411678994</v>
+        <v>541782.0711540411</v>
       </c>
       <c r="R53" t="n">
-        <v>7208389.51064281</v>
+        <v>7208416.248932831</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6517,7 +6507,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6527,7 +6517,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6554,10 +6544,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>104660081</v>
+        <v>104660076</v>
       </c>
       <c r="B54" t="n">
-        <v>89410</v>
+        <v>89406</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6570,21 +6560,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6594,10 +6584,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542027.5024151764</v>
+        <v>542025.1040125923</v>
       </c>
       <c r="R54" t="n">
-        <v>7208529.306604995</v>
+        <v>7208549.162598849</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6629,7 +6619,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6629,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,10 +6656,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>104660073</v>
+        <v>104660056</v>
       </c>
       <c r="B55" t="n">
-        <v>77588</v>
+        <v>73693</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6682,21 +6672,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6706,10 +6696,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541782.0711540411</v>
+        <v>542467.4800613892</v>
       </c>
       <c r="R55" t="n">
-        <v>7208416.248932831</v>
+        <v>7208754.746082969</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6741,7 +6731,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6741,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6778,10 +6768,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>104660076</v>
+        <v>104660054</v>
       </c>
       <c r="B56" t="n">
-        <v>89406</v>
+        <v>73693</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6794,21 +6784,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6818,10 +6808,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>542025.1040125923</v>
+        <v>542049.0111340873</v>
       </c>
       <c r="R56" t="n">
-        <v>7208549.162598849</v>
+        <v>7208566.427107241</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6853,7 +6843,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6863,7 +6853,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6890,10 +6880,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>104660056</v>
+        <v>104660061</v>
       </c>
       <c r="B57" t="n">
-        <v>73693</v>
+        <v>56395</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6906,34 +6896,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bladberget, Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>542467.4800613892</v>
+        <v>542000.0207586873</v>
       </c>
       <c r="R57" t="n">
-        <v>7208754.746082969</v>
+        <v>7208495.064014736</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6965,7 +6960,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6975,7 +6970,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7002,10 +6997,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>104660054</v>
+        <v>104660086</v>
       </c>
       <c r="B58" t="n">
-        <v>73693</v>
+        <v>77506</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7018,21 +7013,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7042,10 +7037,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>542049.0111340873</v>
+        <v>542282.8641733872</v>
       </c>
       <c r="R58" t="n">
-        <v>7208566.427107241</v>
+        <v>7208747.466893868</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7077,7 +7072,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7087,7 +7082,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7114,10 +7109,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>104660061</v>
+        <v>104660064</v>
       </c>
       <c r="B59" t="n">
-        <v>56395</v>
+        <v>78596</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7126,46 +7121,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bladberget, Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>542000.0207586873</v>
+        <v>542377.7157996765</v>
       </c>
       <c r="R59" t="n">
-        <v>7208495.064014736</v>
+        <v>7208810.594455929</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7194,7 +7184,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7204,7 +7194,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7231,7 +7221,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>104660086</v>
+        <v>104660083</v>
       </c>
       <c r="B60" t="n">
         <v>77506</v>
@@ -7271,10 +7261,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>542282.8641733872</v>
+        <v>541967.1311408941</v>
       </c>
       <c r="R60" t="n">
-        <v>7208747.466893868</v>
+        <v>7208393.455902003</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7306,7 +7296,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7316,7 +7306,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7343,10 +7333,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>104660064</v>
+        <v>104660077</v>
       </c>
       <c r="B61" t="n">
-        <v>78596</v>
+        <v>89410</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7355,25 +7345,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7383,13 +7373,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>542377.7157996765</v>
+        <v>541812.8665031057</v>
       </c>
       <c r="R61" t="n">
-        <v>7208810.594455929</v>
+        <v>7208516.555098962</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7418,7 +7408,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7428,7 +7418,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7455,10 +7445,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>104660083</v>
+        <v>104660078</v>
       </c>
       <c r="B62" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7471,21 +7461,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7495,10 +7485,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541967.1311408941</v>
+        <v>541904.0426847516</v>
       </c>
       <c r="R62" t="n">
-        <v>7208393.455902003</v>
+        <v>7208329.933114159</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7530,7 +7520,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7540,7 +7530,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7567,10 +7557,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>104660077</v>
+        <v>104660057</v>
       </c>
       <c r="B63" t="n">
-        <v>89410</v>
+        <v>89356</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7579,25 +7569,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7607,10 +7597,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541812.8665031057</v>
+        <v>542424.7325339405</v>
       </c>
       <c r="R63" t="n">
-        <v>7208516.555098962</v>
+        <v>7208811.263258211</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7642,7 +7632,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7652,7 +7642,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7679,10 +7669,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>104660078</v>
+        <v>104660067</v>
       </c>
       <c r="B64" t="n">
-        <v>89410</v>
+        <v>56411</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7695,34 +7685,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bladberget, Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541904.0426847516</v>
+        <v>542314.4551710433</v>
       </c>
       <c r="R64" t="n">
-        <v>7208329.933114159</v>
+        <v>7208670.899224089</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7754,7 +7749,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7764,7 +7759,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7791,10 +7786,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>104660057</v>
+        <v>104660072</v>
       </c>
       <c r="B65" t="n">
-        <v>89356</v>
+        <v>77588</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7803,25 +7798,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>864</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7831,10 +7826,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542424.7325339405</v>
+        <v>542367.7491595935</v>
       </c>
       <c r="R65" t="n">
-        <v>7208811.263258211</v>
+        <v>7208736.823688965</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7866,7 +7861,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7876,7 +7871,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7903,10 +7898,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>104660067</v>
+        <v>104660075</v>
       </c>
       <c r="B66" t="n">
-        <v>56411</v>
+        <v>89406</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7919,39 +7914,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bladberget, Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>542314.4551710433</v>
+        <v>541781.2772625567</v>
       </c>
       <c r="R66" t="n">
-        <v>7208670.899224089</v>
+        <v>7208412.428971238</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7983,7 +7973,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7993,7 +7983,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8020,10 +8010,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>104660072</v>
+        <v>104660079</v>
       </c>
       <c r="B67" t="n">
-        <v>77588</v>
+        <v>89410</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8036,21 +8026,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8060,10 +8050,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>542367.7491595935</v>
+        <v>541970.1084873448</v>
       </c>
       <c r="R67" t="n">
-        <v>7208736.823688965</v>
+        <v>7208392.651399266</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8095,7 +8085,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8105,7 +8095,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8132,10 +8122,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>104660075</v>
+        <v>104660055</v>
       </c>
       <c r="B68" t="n">
-        <v>89406</v>
+        <v>73693</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8148,21 +8138,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8172,10 +8162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541781.2772625567</v>
+        <v>542117.5213644229</v>
       </c>
       <c r="R68" t="n">
-        <v>7208412.428971238</v>
+        <v>7208605.480541566</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8207,7 +8197,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8217,7 +8207,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8244,10 +8234,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>104660079</v>
+        <v>104660085</v>
       </c>
       <c r="B69" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8260,21 +8250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8284,10 +8274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541970.1084873448</v>
+        <v>542092.9350115185</v>
       </c>
       <c r="R69" t="n">
-        <v>7208392.651399266</v>
+        <v>7208576.357013171</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8319,7 +8309,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8329,7 +8319,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8356,10 +8346,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>104660055</v>
+        <v>104660082</v>
       </c>
       <c r="B70" t="n">
-        <v>73693</v>
+        <v>77506</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8372,21 +8362,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8396,10 +8386,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>542117.5213644229</v>
+        <v>541822.1550578115</v>
       </c>
       <c r="R70" t="n">
-        <v>7208605.480541566</v>
+        <v>7208337.670818017</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8431,7 +8421,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8441,7 +8431,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8468,10 +8458,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>104660085</v>
+        <v>104660065</v>
       </c>
       <c r="B71" t="n">
-        <v>77506</v>
+        <v>56411</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8484,34 +8474,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bladberget, Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>542092.9350115185</v>
+        <v>541985.9264890314</v>
       </c>
       <c r="R71" t="n">
-        <v>7208576.357013171</v>
+        <v>7208412.764827228</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8543,7 +8538,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8553,7 +8548,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8580,10 +8575,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>104660082</v>
+        <v>104660058</v>
       </c>
       <c r="B72" t="n">
-        <v>77506</v>
+        <v>89356</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8592,25 +8587,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8620,10 +8615,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541822.1550578115</v>
+        <v>542253.8048515412</v>
       </c>
       <c r="R72" t="n">
-        <v>7208337.670818017</v>
+        <v>7208735.206364101</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8655,7 +8650,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8665,7 +8660,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8692,10 +8687,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>104660065</v>
+        <v>104660088</v>
       </c>
       <c r="B73" t="n">
-        <v>56411</v>
+        <v>77506</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8708,39 +8703,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bladberget, Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>541985.9264890314</v>
+        <v>542402.9789057968</v>
       </c>
       <c r="R73" t="n">
-        <v>7208412.764827228</v>
+        <v>7208732.246685387</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8772,7 +8762,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8782,7 +8772,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8809,10 +8799,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>104660058</v>
+        <v>104660084</v>
       </c>
       <c r="B74" t="n">
-        <v>89356</v>
+        <v>77506</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8821,25 +8811,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8849,10 +8839,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>542253.8048515412</v>
+        <v>542006.6138428586</v>
       </c>
       <c r="R74" t="n">
-        <v>7208735.206364101</v>
+        <v>7208508.275877368</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8884,7 +8874,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8894,7 +8884,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8921,10 +8911,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>104660088</v>
+        <v>104660053</v>
       </c>
       <c r="B75" t="n">
-        <v>77506</v>
+        <v>73693</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8937,21 +8927,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8961,10 +8951,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>542402.9789057968</v>
+        <v>541803.4710103488</v>
       </c>
       <c r="R75" t="n">
-        <v>7208732.246685387</v>
+        <v>7208461.408182736</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8996,7 +8986,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9006,7 +8996,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9033,10 +9023,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>104660084</v>
+        <v>104660060</v>
       </c>
       <c r="B76" t="n">
-        <v>77506</v>
+        <v>56395</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9049,34 +9039,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bladberget, Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>542006.6138428586</v>
+        <v>541944.4335299737</v>
       </c>
       <c r="R76" t="n">
-        <v>7208508.275877368</v>
+        <v>7208380.440223145</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9108,7 +9103,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9118,7 +9113,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9145,10 +9140,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>104660053</v>
+        <v>121087295</v>
       </c>
       <c r="B77" t="n">
-        <v>73693</v>
+        <v>90710</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9161,34 +9156,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Bladberget, Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>541803.4710103488</v>
+        <v>541831</v>
       </c>
       <c r="R77" t="n">
-        <v>7208461.408182736</v>
+        <v>7208244</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9215,22 +9210,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9245,22 +9240,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>104660060</v>
+        <v>121086346</v>
       </c>
       <c r="B78" t="n">
-        <v>56395</v>
+        <v>55953</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9273,42 +9268,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bladberget, Rödingsjön, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>541944.4335299737</v>
+        <v>541868</v>
       </c>
       <c r="R78" t="n">
-        <v>7208380.440223145</v>
+        <v>7208253</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9332,22 +9326,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9362,22 +9356,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström, Nils Åslund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121087295</v>
+        <v>121087306</v>
       </c>
       <c r="B79" t="n">
-        <v>90710</v>
+        <v>91065</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9386,25 +9380,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9414,10 +9408,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541831</v>
+        <v>541965</v>
       </c>
       <c r="R79" t="n">
-        <v>7208244</v>
+        <v>7208367</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9449,7 +9443,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9459,7 +9453,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9486,10 +9480,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121086346</v>
+        <v>121087308</v>
       </c>
       <c r="B80" t="n">
-        <v>55953</v>
+        <v>90706</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9502,41 +9496,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>206004</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541868</v>
+        <v>541971</v>
       </c>
       <c r="R80" t="n">
-        <v>7208253</v>
+        <v>7208368</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9565,7 +9555,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9575,7 +9565,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9590,22 +9580,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121087306</v>
+        <v>121087421</v>
       </c>
       <c r="B81" t="n">
-        <v>91065</v>
+        <v>57351</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9614,41 +9604,49 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541965</v>
+        <v>541876</v>
       </c>
       <c r="R81" t="n">
-        <v>7208367</v>
+        <v>7208263</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9677,7 +9675,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9687,7 +9685,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9702,22 +9700,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121087308</v>
+        <v>121087292</v>
       </c>
       <c r="B82" t="n">
-        <v>90706</v>
+        <v>90724</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9730,21 +9728,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9754,10 +9752,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541971</v>
+        <v>541850</v>
       </c>
       <c r="R82" t="n">
-        <v>7208368</v>
+        <v>7208245</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9789,7 +9787,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9799,7 +9797,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9826,10 +9824,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121087421</v>
+        <v>121087298</v>
       </c>
       <c r="B83" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9842,45 +9840,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>541876</v>
+        <v>541890</v>
       </c>
       <c r="R83" t="n">
-        <v>7208263</v>
+        <v>7208300</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9909,7 +9899,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9919,7 +9909,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9934,22 +9924,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121087292</v>
+        <v>121087304</v>
       </c>
       <c r="B84" t="n">
-        <v>90724</v>
+        <v>57351</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9962,34 +9952,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>541850</v>
+        <v>541955</v>
       </c>
       <c r="R84" t="n">
-        <v>7208245</v>
+        <v>7208354</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10021,7 +10016,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10031,7 +10026,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10058,10 +10053,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121087298</v>
+        <v>121087300</v>
       </c>
       <c r="B85" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10074,34 +10069,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541890</v>
+        <v>541932</v>
       </c>
       <c r="R85" t="n">
-        <v>7208300</v>
+        <v>7208314</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10170,7 +10170,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121087304</v>
+        <v>121087303</v>
       </c>
       <c r="B86" t="n">
         <v>57351</v>
@@ -10206,7 +10206,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10215,10 +10215,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541955</v>
+        <v>541947</v>
       </c>
       <c r="R86" t="n">
-        <v>7208354</v>
+        <v>7208367</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10287,7 +10287,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121087300</v>
+        <v>121087302</v>
       </c>
       <c r="B87" t="n">
         <v>57351</v>
@@ -10332,10 +10332,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541932</v>
+        <v>541945</v>
       </c>
       <c r="R87" t="n">
-        <v>7208314</v>
+        <v>7208373</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10404,10 +10404,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121087303</v>
+        <v>121087307</v>
       </c>
       <c r="B88" t="n">
-        <v>57351</v>
+        <v>91150</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10416,43 +10416,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541947</v>
+        <v>541966</v>
       </c>
       <c r="R88" t="n">
-        <v>7208367</v>
+        <v>7208365</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10484,7 +10479,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10494,7 +10489,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10521,10 +10516,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121087302</v>
+        <v>121087299</v>
       </c>
       <c r="B89" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10537,39 +10532,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541945</v>
+        <v>541906</v>
       </c>
       <c r="R89" t="n">
-        <v>7208373</v>
+        <v>7208324</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10601,7 +10591,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10611,7 +10601,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10638,10 +10628,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121087307</v>
+        <v>121086332</v>
       </c>
       <c r="B90" t="n">
-        <v>91150</v>
+        <v>57351</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10650,41 +10640,49 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541966</v>
+        <v>541849</v>
       </c>
       <c r="R90" t="n">
-        <v>7208365</v>
+        <v>7208291</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10713,7 +10711,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10723,7 +10721,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10734,26 +10737,46 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121087299</v>
+        <v>121087294</v>
       </c>
       <c r="B91" t="n">
-        <v>90728</v>
+        <v>90724</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10766,21 +10789,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10790,10 +10813,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541906</v>
+        <v>541831</v>
       </c>
       <c r="R91" t="n">
-        <v>7208324</v>
+        <v>7208244</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10825,7 +10848,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10835,7 +10858,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10862,7 +10885,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121086332</v>
+        <v>121087293</v>
       </c>
       <c r="B92" t="n">
         <v>57351</v>
@@ -10896,27 +10919,24 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541849</v>
+        <v>541831</v>
       </c>
       <c r="R92" t="n">
-        <v>7208291</v>
+        <v>7208244</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10945,7 +10965,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10955,12 +10975,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10971,46 +10986,26 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121087294</v>
+        <v>121087305</v>
       </c>
       <c r="B93" t="n">
-        <v>90724</v>
+        <v>90710</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11023,21 +11018,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11047,10 +11042,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541831</v>
+        <v>541965</v>
       </c>
       <c r="R93" t="n">
-        <v>7208244</v>
+        <v>7208372</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11082,7 +11077,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11092,7 +11087,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11119,7 +11114,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121087293</v>
+        <v>121086333</v>
       </c>
       <c r="B94" t="n">
         <v>57351</v>
@@ -11153,24 +11148,27 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541831</v>
+        <v>541904</v>
       </c>
       <c r="R94" t="n">
-        <v>7208244</v>
+        <v>7208324</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11199,7 +11197,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11209,7 +11207,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11220,26 +11223,46 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121087305</v>
+        <v>121087301</v>
       </c>
       <c r="B95" t="n">
-        <v>90710</v>
+        <v>57351</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11252,34 +11275,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541965</v>
+        <v>541941</v>
       </c>
       <c r="R95" t="n">
-        <v>7208372</v>
+        <v>7208347</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11311,7 +11339,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11321,7 +11349,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11348,10 +11376,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121086333</v>
+        <v>121087297</v>
       </c>
       <c r="B96" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11364,45 +11392,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541904</v>
+        <v>541887</v>
       </c>
       <c r="R96" t="n">
-        <v>7208324</v>
+        <v>7208302</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11431,7 +11451,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11441,12 +11461,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11457,268 +11472,19 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>121087301</v>
-      </c>
-      <c r="B97" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Rödingtjärnen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>541941</v>
-      </c>
-      <c r="R97" t="n">
-        <v>7208347</v>
-      </c>
-      <c r="S97" t="n">
-        <v>25</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2024-11-08</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2024-11-08</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>121087297</v>
-      </c>
-      <c r="B98" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Rödingtjärnen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>541887</v>
-      </c>
-      <c r="R98" t="n">
-        <v>7208302</v>
-      </c>
-      <c r="S98" t="n">
-        <v>25</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>2024-11-08</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2024-11-08</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT98" t="inlineStr"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
